--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484614_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484614_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.8869</v>
+        <v>4.3777</v>
       </c>
       <c r="E2" t="n">
-        <v>3.2646</v>
+        <v>3.3747</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6223</v>
+        <v>1.003</v>
       </c>
       <c r="G2" t="n">
         <v>-0.1104</v>
@@ -610,13 +610,13 @@
         <v>3.8484</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7982</v>
+        <v>0.289</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1493</v>
+        <v>-0.0392</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9475</v>
+        <v>0.3282</v>
       </c>
       <c r="V2" t="n">
         <v>1.267</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0119</v>
+        <v>1.7479</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0377</v>
+        <v>-0.0788</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0496</v>
+        <v>1.8266</v>
       </c>
       <c r="G3" t="n">
         <v>0.2177</v>
@@ -688,13 +688,13 @@
         <v>1.2828</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8046</v>
+        <v>0.5405</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0717</v>
+        <v>0.0306</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7329</v>
+        <v>0.51</v>
       </c>
       <c r="V3" t="n">
         <v>0.6231</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3215</v>
+        <v>1.1322</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.8653</v>
+        <v>-1.1538</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1869</v>
+        <v>2.2859</v>
       </c>
       <c r="G4" t="n">
         <v>-0.4407</v>
@@ -766,13 +766,13 @@
         <v>1.6493</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0842</v>
+        <v>-0.1052</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1267</v>
+        <v>-0.1617</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0426</v>
+        <v>0.0565</v>
       </c>
       <c r="V4" t="n">
         <v>0.945</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3664</v>
+        <v>0.101</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0375</v>
+        <v>0.306</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3288</v>
+        <v>-0.205</v>
       </c>
       <c r="G5" t="n">
         <v>-1.621</v>
@@ -844,13 +844,13 @@
         <v>1.0995</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1565</v>
+        <v>0.3109</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1659</v>
+        <v>0.1776</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0094</v>
+        <v>0.1333</v>
       </c>
       <c r="V5" t="n">
         <v>0.3115</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.2654</v>
+        <v>-1.092</v>
       </c>
       <c r="E6" t="n">
         <v>-1.8379</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5725</v>
+        <v>0.7459</v>
       </c>
       <c r="G6" t="n">
         <v>-0.4278</v>
@@ -922,13 +922,13 @@
         <v>1.0995</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0209</v>
+        <v>-0.8475</v>
       </c>
       <c r="T6" t="n">
         <v>-0.3673</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6536</v>
+        <v>-0.4802</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.8338</v>
+        <v>-1.3416</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.5906</v>
+        <v>-2.2471</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7568</v>
+        <v>0.9055</v>
       </c>
       <c r="G7" t="n">
         <v>-1.5454</v>
@@ -1000,13 +1000,13 @@
         <v>2.5656</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.2938</v>
+        <v>-0.8017</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.0467</v>
+        <v>-0.7032</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2471</v>
+        <v>-0.0984</v>
       </c>
       <c r="V7" t="n">
         <v>-0.6439</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.744</v>
+        <v>-2.5898</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.4664</v>
+        <v>-4.4113</v>
       </c>
       <c r="F8" t="n">
-        <v>1.7224</v>
+        <v>1.8215</v>
       </c>
       <c r="G8" t="n">
         <v>-2.4715</v>
@@ -1078,13 +1078,13 @@
         <v>2.9321</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4845</v>
+        <v>-0.3303</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3876</v>
+        <v>-0.3325</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0969</v>
+        <v>0.0022</v>
       </c>
       <c r="V8" t="n">
         <v>0.945</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.4779</v>
+        <v>-3.4942</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.8392</v>
+        <v>-4.8803</v>
       </c>
       <c r="F9" t="n">
-        <v>1.3613</v>
+        <v>1.386</v>
       </c>
       <c r="G9" t="n">
         <v>-3.9341</v>
@@ -1156,13 +1156,13 @@
         <v>2.5656</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2768</v>
+        <v>-0.2932</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1674</v>
+        <v>-0.2085</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1095</v>
+        <v>-0.0847</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.6619</v>
+        <v>-3.6756</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.2162</v>
+        <v>-5.1061</v>
       </c>
       <c r="F10" t="n">
-        <v>1.5543</v>
+        <v>1.4305</v>
       </c>
       <c r="G10" t="n">
         <v>-0.9852</v>
@@ -1234,13 +1234,13 @@
         <v>1.8326</v>
       </c>
       <c r="S10" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.0688</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3506</v>
+        <v>-0.2405</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4332</v>
+        <v>0.3094</v>
       </c>
       <c r="V10" t="n">
         <v>-0.0104</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.4466</v>
+        <v>-5.1904</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.0414</v>
+        <v>-6.0825</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5948</v>
+        <v>0.8921</v>
       </c>
       <c r="G11" t="n">
         <v>-3.7089</v>
@@ -1312,13 +1312,13 @@
         <v>2.1991</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5544</v>
+        <v>-0.2983</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0347</v>
+        <v>-0.0064</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5891</v>
+        <v>-0.2919</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6335</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-10.5757</v>
+        <v>-10.0248</v>
       </c>
       <c r="E12" t="n">
-        <v>-22.6676</v>
+        <v>-22.1171</v>
       </c>
       <c r="F12" t="n">
-        <v>12.0921</v>
+        <v>12.092</v>
       </c>
       <c r="G12" t="n">
         <v>-15.0273</v>
@@ -1390,13 +1390,13 @@
         <v>21.0745</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.0173</v>
+        <v>-1.467</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.4017</v>
+        <v>-1.8511</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3842000000000003</v>
+        <v>0.3844</v>
       </c>
       <c r="V12" t="n">
         <v>2.8038</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. NEBOT GARCIA</t>
+          <t>P. ARISTA CALLAU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.291</v>
+        <v>3.8361</v>
       </c>
       <c r="E13" t="n">
-        <v>2.3539</v>
+        <v>-3.2854</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9372</v>
+        <v>7.1215</v>
       </c>
       <c r="G13" t="n">
-        <v>1.5746</v>
+        <v>5.2743</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5617</v>
+        <v>5.1687</v>
       </c>
       <c r="I13" t="n">
-        <v>1.0129</v>
+        <v>0.1056</v>
       </c>
       <c r="J13" t="n">
-        <v>1.7763</v>
+        <v>2.9152</v>
       </c>
       <c r="K13" t="n">
-        <v>0.4427</v>
+        <v>3.3221</v>
       </c>
       <c r="L13" t="n">
-        <v>1.3336</v>
+        <v>-0.4069</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.2017</v>
+        <v>2.3591</v>
       </c>
       <c r="N13" t="n">
-        <v>0.119</v>
+        <v>1.8466</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.3207</v>
+        <v>0.5125</v>
       </c>
       <c r="P13" t="n">
-        <v>0.733</v>
+        <v>-1.2828</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-4.7647</v>
       </c>
       <c r="R13" t="n">
-        <v>0.733</v>
+        <v>3.4819</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6615</v>
+        <v>1.0907</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2557</v>
+        <v>-0.2002</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4058</v>
+        <v>1.2909</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3219</v>
+        <v>-1.2461</v>
       </c>
       <c r="W13" t="n">
-        <v>0.3219</v>
+        <v>-1.2357</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0.0104</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. ARISTA CALLAU</t>
+          <t>C. WHITSON</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.6604</v>
+        <v>3.2984</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.7662</v>
+        <v>-0.6808</v>
       </c>
       <c r="F14" t="n">
-        <v>6.4266</v>
+        <v>3.9792</v>
       </c>
       <c r="G14" t="n">
-        <v>5.2743</v>
+        <v>2.285</v>
       </c>
       <c r="H14" t="n">
-        <v>5.1687</v>
+        <v>0.3229</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1056</v>
+        <v>1.9622</v>
       </c>
       <c r="J14" t="n">
-        <v>2.9152</v>
+        <v>0.8856000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>3.3221</v>
+        <v>-0.4676</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.4069</v>
+        <v>1.3533</v>
       </c>
       <c r="M14" t="n">
-        <v>2.3591</v>
+        <v>1.3994</v>
       </c>
       <c r="N14" t="n">
-        <v>1.8466</v>
+        <v>0.7905</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5125</v>
+        <v>0.6089</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.2828</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q14" t="n">
-        <v>-4.7647</v>
+        <v>-2.7489</v>
       </c>
       <c r="R14" t="n">
-        <v>3.4819</v>
+        <v>2.1991</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.08500000000000001</v>
+        <v>0.9297</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.681</v>
+        <v>0.227</v>
       </c>
       <c r="U14" t="n">
-        <v>0.596</v>
+        <v>0.7027</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.2461</v>
+        <v>0.6335</v>
       </c>
       <c r="W14" t="n">
-        <v>-1.2357</v>
+        <v>0.9554</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.0104</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C. WHITSON</t>
+          <t>M. NEBOT GARCIA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4694</v>
+        <v>3.0099</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.8731</v>
+        <v>1.9693</v>
       </c>
       <c r="F15" t="n">
-        <v>3.3425</v>
+        <v>1.0406</v>
       </c>
       <c r="G15" t="n">
-        <v>2.285</v>
+        <v>1.5746</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3229</v>
+        <v>0.5617</v>
       </c>
       <c r="I15" t="n">
-        <v>1.9622</v>
+        <v>1.0129</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8856000000000001</v>
+        <v>1.7763</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.4676</v>
+        <v>0.4427</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3533</v>
+        <v>1.3336</v>
       </c>
       <c r="M15" t="n">
-        <v>1.3994</v>
+        <v>-0.2017</v>
       </c>
       <c r="N15" t="n">
-        <v>0.7905</v>
+        <v>0.119</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6089</v>
+        <v>-0.3207</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.5498</v>
+        <v>0.733</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.7489</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1991</v>
+        <v>0.733</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1007</v>
+        <v>0.3803</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0347</v>
+        <v>-0.129</v>
       </c>
       <c r="U15" t="n">
-        <v>0.066</v>
+        <v>0.5092</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6335</v>
+        <v>0.3219</v>
       </c>
       <c r="W15" t="n">
-        <v>0.9554</v>
+        <v>0.3219</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. ARIJA DE LA PEÑA</t>
+          <t>C. FUSTER ROYO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9005</v>
+        <v>2.1045</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9005</v>
+        <v>1.2288</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>0.8757</v>
       </c>
       <c r="G16" t="n">
-        <v>1.9005</v>
+        <v>1.3867</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6502</v>
+        <v>-0.7097</v>
       </c>
       <c r="I16" t="n">
-        <v>1.2502</v>
+        <v>2.0964</v>
       </c>
       <c r="J16" t="n">
-        <v>1.9005</v>
+        <v>1.4769</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6502</v>
+        <v>-0.5235</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2502</v>
+        <v>2.0004</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>-0.0902</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>-0.1863</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>0.0961</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>0.9163</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>0.9163</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>0.1235</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>-0.2481</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>0.3716</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. ALBA GONZALEZ</t>
+          <t>D. ARIJA DE LA PEÑA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.8322</v>
+        <v>1.9005</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.3473</v>
+        <v>1.9005</v>
       </c>
       <c r="F17" t="n">
-        <v>3.1795</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1014</v>
+        <v>1.9005</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.867</v>
+        <v>0.6502</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9684</v>
+        <v>1.2502</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.9439</v>
+        <v>1.9005</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.0469</v>
+        <v>0.6502</v>
       </c>
       <c r="L17" t="n">
-        <v>0.103</v>
+        <v>1.2502</v>
       </c>
       <c r="M17" t="n">
-        <v>1.0453</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1799</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0.8653</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.5498</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.9321</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3823</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3355</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1.2617</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0738</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>0.945</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. DIAGNE</t>
+          <t>A. ALBA GONZALEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.6556</v>
+        <v>1.6326</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.5122</v>
+        <v>-2.2127</v>
       </c>
       <c r="F18" t="n">
-        <v>3.1678</v>
+        <v>3.8453</v>
       </c>
       <c r="G18" t="n">
-        <v>3.5804</v>
+        <v>0.1014</v>
       </c>
       <c r="H18" t="n">
-        <v>2.7504</v>
+        <v>-0.867</v>
       </c>
       <c r="I18" t="n">
-        <v>0.83</v>
+        <v>0.9684</v>
       </c>
       <c r="J18" t="n">
-        <v>2.3109</v>
+        <v>-0.9439</v>
       </c>
       <c r="K18" t="n">
-        <v>2.1858</v>
+        <v>-1.0469</v>
       </c>
       <c r="L18" t="n">
-        <v>0.125</v>
+        <v>0.103</v>
       </c>
       <c r="M18" t="n">
-        <v>1.2695</v>
+        <v>1.0453</v>
       </c>
       <c r="N18" t="n">
-        <v>0.5646</v>
+        <v>0.1799</v>
       </c>
       <c r="O18" t="n">
-        <v>0.705</v>
+        <v>0.8653</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.5656</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q18" t="n">
-        <v>-4.7647</v>
+        <v>-2.9321</v>
       </c>
       <c r="R18" t="n">
-        <v>2.1991</v>
+        <v>2.3823</v>
       </c>
       <c r="S18" t="n">
-        <v>1.5754</v>
+        <v>1.1359</v>
       </c>
       <c r="T18" t="n">
-        <v>1.5543</v>
+        <v>0.3963</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0211</v>
+        <v>0.7396</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.9346</v>
+        <v>0.945</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.6127</v>
+        <v>1.267</v>
       </c>
       <c r="X18" t="n">
         <v>-0.3219</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. FUSTER ROYO</t>
+          <t>E. DIAGNE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.4329</v>
+        <v>1.1107</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0365</v>
+        <v>-2.5699</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3964</v>
+        <v>3.6806</v>
       </c>
       <c r="G19" t="n">
-        <v>1.3867</v>
+        <v>3.5804</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.7097</v>
+        <v>2.7504</v>
       </c>
       <c r="I19" t="n">
-        <v>2.0964</v>
+        <v>0.83</v>
       </c>
       <c r="J19" t="n">
-        <v>1.4769</v>
+        <v>2.3109</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5235</v>
+        <v>2.1858</v>
       </c>
       <c r="L19" t="n">
-        <v>2.0004</v>
+        <v>0.125</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0902</v>
+        <v>1.2695</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1863</v>
+        <v>0.5646</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0961</v>
+        <v>0.705</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9163</v>
+        <v>-2.5656</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-4.7647</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9163</v>
+        <v>2.1991</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5482</v>
+        <v>1.0305</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4404</v>
+        <v>0.4966</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1078</v>
+        <v>0.5339</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3219</v>
+        <v>-0.9346</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.6127</v>
       </c>
       <c r="X19" t="n">
         <v>-0.3219</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6491</v>
+        <v>0.8165</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.8168</v>
+        <v>-1.336</v>
       </c>
       <c r="F20" t="n">
-        <v>2.4659</v>
+        <v>2.1526</v>
       </c>
       <c r="G20" t="n">
         <v>-0.4656</v>
@@ -2014,13 +2014,13 @@
         <v>1.8326</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4105</v>
+        <v>0.5779</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.101</v>
+        <v>-0.6203</v>
       </c>
       <c r="U20" t="n">
-        <v>1.5115</v>
+        <v>1.1981</v>
       </c>
       <c r="V20" t="n">
         <v>-0.945</v>
@@ -2047,10 +2047,10 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2095</v>
+        <v>0.3057</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0598</v>
+        <v>0.1559</v>
       </c>
       <c r="F21" t="n">
         <v>0.1498</v>
@@ -2092,10 +2092,10 @@
         <v>0.1833</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0732</v>
+        <v>0.1693</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0181</v>
+        <v>0.1143</v>
       </c>
       <c r="U21" t="n">
         <v>0.0551</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. IGUAL BAU</t>
+          <t>D. ARIJA DE LA PENA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.1102</v>
+        <v>-0.1643</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.0047</v>
+        <v>-3.6086</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1055</v>
+        <v>3.4443</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2292</v>
+        <v>1.9296</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.0272</v>
+        <v>0.9841</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2564</v>
+        <v>0.9455</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0217</v>
+        <v>1.1578</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0217</v>
+        <v>0.3402</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>0.8176</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2075</v>
+        <v>0.7718</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.0489</v>
+        <v>0.6439</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2564</v>
+        <v>0.1279</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.9163</v>
+        <v>-2.0158</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9163</v>
+        <v>-4.5814</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.5656</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4232</v>
+        <v>0.8565</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1101</v>
+        <v>0.1162</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.313</v>
+        <v>0.7403</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.9346</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.3011</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.6335</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. ARIJA DE LA PENA</t>
+          <t>D. IGUAL BAU</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.5061</v>
+        <v>-0.9572000000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.1855</v>
+        <v>-1.0047</v>
       </c>
       <c r="F23" t="n">
-        <v>2.6794</v>
+        <v>0.0475</v>
       </c>
       <c r="G23" t="n">
-        <v>1.9296</v>
+        <v>0.2292</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9841</v>
+        <v>-0.0272</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9455</v>
+        <v>0.2564</v>
       </c>
       <c r="J23" t="n">
-        <v>1.1578</v>
+        <v>0.0217</v>
       </c>
       <c r="K23" t="n">
-        <v>0.3402</v>
+        <v>0.0217</v>
       </c>
       <c r="L23" t="n">
-        <v>0.8176</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.7718</v>
+        <v>0.2075</v>
       </c>
       <c r="N23" t="n">
-        <v>0.6439</v>
+        <v>-0.0489</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1279</v>
+        <v>0.2564</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.0158</v>
+        <v>-0.9163</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.5814</v>
+        <v>-0.9163</v>
       </c>
       <c r="R23" t="n">
-        <v>2.5656</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4853</v>
+        <v>-0.2702</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4608</v>
+        <v>-0.1101</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0245</v>
+        <v>-0.1601</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.9346</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.3011</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.6335</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.9087</v>
+        <v>-2.4716</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.937</v>
+        <v>-2.6485</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0283</v>
+        <v>0.1769</v>
       </c>
       <c r="G24" t="n">
         <v>-2.7221</v>
@@ -2326,13 +2326,13 @@
         <v>0.9163</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5977</v>
+        <v>-0.1606</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7157</v>
+        <v>-0.4272</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1179</v>
+        <v>0.2666</v>
       </c>
       <c r="V24" t="n">
         <v>-0.3219</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>10.5756</v>
+        <v>14.4218</v>
       </c>
       <c r="E25" t="n">
         <v>-12.0921</v>
       </c>
       <c r="F25" t="n">
-        <v>22.6679</v>
+        <v>26.514</v>
       </c>
       <c r="G25" t="n">
         <v>15.0271</v>
@@ -2374,13 +2374,13 @@
         <v>10.0582</v>
       </c>
       <c r="I25" t="n">
-        <v>4.969100000000001</v>
+        <v>4.969099999999999</v>
       </c>
       <c r="J25" t="n">
         <v>8.6501</v>
       </c>
       <c r="K25" t="n">
-        <v>6.2435</v>
+        <v>6.243500000000001</v>
       </c>
       <c r="L25" t="n">
         <v>2.406499999999999</v>
@@ -2389,7 +2389,7 @@
         <v>6.376999999999999</v>
       </c>
       <c r="N25" t="n">
-        <v>3.8144</v>
+        <v>3.814400000000001</v>
       </c>
       <c r="O25" t="n">
         <v>2.5625</v>
@@ -2404,13 +2404,13 @@
         <v>17.4095</v>
       </c>
       <c r="S25" t="n">
-        <v>2.017399999999999</v>
+        <v>5.8635</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3845000000000001</v>
+        <v>-0.3845</v>
       </c>
       <c r="U25" t="n">
-        <v>2.4019</v>
+        <v>6.247900000000001</v>
       </c>
       <c r="V25" t="n">
         <v>-2.8037</v>
